--- a/artfynd/A 61319-2021 artfynd.xlsx
+++ b/artfynd/A 61319-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61319-2021 artfynd.xlsx
+++ b/artfynd/A 61319-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,68 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99238162</v>
+        <v>98430178</v>
       </c>
       <c r="B2" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101246</v>
+        <v>14</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Klätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Agrostemma githago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stebostigen, Äskestock, Sm</t>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595729.4782491435</v>
+        <v>595696</v>
       </c>
       <c r="R2" t="n">
-        <v>6386598.779332656</v>
+        <v>6386616</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +760,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett tiotal plantor har blommat ut från ängsfröblandning på f.d. åkermark mellan tomten och intilliggande bilväg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,15 +786,2659 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124306634</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hörd ropande västerifrån.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124306591</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115618438</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100041977</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56879</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595696</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-04-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tryckte i ett odlingsröse i vägkanten på andra sidan tomten, mitt under pågående röjning!</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Rebecca Petersen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111290971</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56879</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Väg 60 m NNV Vagnslidret, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595680</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6386572</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Funnen påkörd mitt på asfaltsvägen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115617675</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57825</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100096</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pandion haliaetus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16026646</v>
+      </c>
+      <c r="B9" t="n">
+        <v>9406</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595696</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-06-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-06-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99238162</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9406</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stebostigen, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595729</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6386599</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Rebecca Petersen</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Rebecca Petersen</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>101444897</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5463</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101704</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ekträdlöpare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhagium sycophanta</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schrank, 1781)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595696</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124306326</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115618441</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57105</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hörd nattetid. Möjligen sträck.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132216453</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57585</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gråtrut</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Larus argentatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124305697</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57802</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102975</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Asio otus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ivrigt ropande. Hörd söderut.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115618408</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115618403</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58541</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132216531</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58250</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115618391</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132216532</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132216486</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132216485</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58634</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103046</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gråsiska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Acanthis flammea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>595694</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115621353</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>595696</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Upptäcktes i samband med grävarbeten på tomten.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist, Rebecca Petersen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>98430508</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stenbostigen 2, Äskestock, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>595696</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6386616</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-08-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-08-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
